--- a/Data_Table/뽑기 테이블.xlsx
+++ b/Data_Table/뽑기 테이블.xlsx
@@ -773,7 +773,7 @@
         <v>0.5</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -789,7 +789,7 @@
         <v>0.27</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0.13</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>0</v>
@@ -821,7 +821,7 @@
         <v>0.06</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>0.6</v>
@@ -837,7 +837,7 @@
         <v>0.03</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>0.3</v>
@@ -853,7 +853,7 @@
         <v>0.01</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>0.1</v>

--- a/Data_Table/뽑기 테이블.xlsx
+++ b/Data_Table/뽑기 테이블.xlsx
@@ -773,7 +773,7 @@
         <v>0.5</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -789,7 +789,7 @@
         <v>0.27</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0.13</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>0</v>
@@ -821,7 +821,7 @@
         <v>0.06</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>0.6</v>
@@ -837,7 +837,7 @@
         <v>0.03</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>0.3</v>
@@ -853,7 +853,7 @@
         <v>0.01</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>0.1</v>

--- a/Data_Table/뽑기 테이블.xlsx
+++ b/Data_Table/뽑기 테이블.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gacha_Config" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gacha_Grade" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Desc" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Gacha_Config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gacha_Grade" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Column_Desc" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -674,6 +674,21 @@
       <c r="C16" s="1" t="inlineStr">
         <is>
           <t>뽑기 기록 보관 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>shard_full_tier</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>조각 수 = shard_count × 훈장 ÷ 이 값 (이 훈장에서 테이블 값, 최소 1, 2026-10-21)</t>
         </is>
       </c>
     </row>

--- a/Data_Table/뽑기 테이블.xlsx
+++ b/Data_Table/뽑기 테이블.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Gacha_Config" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gacha_Grade" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Column_Desc" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gacha_Config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gacha_Grade" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column_Desc" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
